--- a/submission/제출완료/인종_속도는벡터_조현빈_팀내참여도조사.xlsx
+++ b/submission/제출완료/인종_속도는벡터_조현빈_팀내참여도조사.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hyunbin/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hyunbin/Capstone/submission/제출완료/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B12B2075-BD32-0E47-B688-E26B86F58AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B5FF9B-62E0-ED42-8856-BC863153B1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="20480" windowHeight="20780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -790,13 +790,13 @@
         <v>7</v>
       </c>
       <c r="D8" s="15">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E8" s="15" t="s">
         <v>6</v>
       </c>
       <c r="F8" s="14">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
@@ -820,13 +820,13 @@
         <v>8</v>
       </c>
       <c r="D10" s="14">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>9</v>
       </c>
       <c r="F10" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="17">
